--- a/navneleg-demo/periodic-table/periodisk_tabel_demo.xlsx
+++ b/navneleg-demo/periodic-table/periodisk_tabel_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Periodisk tabel" sheetId="1" r:id="R06e6bdefde0743b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Periodisk tabel" sheetId="1" r:id="R376692e1c723487f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1D4ED8"/>
+        <x:fgColor rgb="FF2563EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -78,24 +78,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PeriodisktabelTable" displayName="PeriodisktabelTable" ref="A1:J26" headerRowCount="1">
-  <x:tableColumns count="10">
-    <x:tableColumn id="1" name="KortID"/>
-    <x:tableColumn id="2" name="Billedfil"/>
-    <x:tableColumn id="3" name="Billedsti"/>
-    <x:tableColumn id="4" name="Symbol"/>
-    <x:tableColumn id="5" name="AtomicNumber"/>
-    <x:tableColumn id="6" name="English"/>
-    <x:tableColumn id="7" name="Dansk"/>
-    <x:tableColumn id="8" name="Group"/>
-    <x:tableColumn id="9" name="Hint"/>
-    <x:tableColumn id="10" name="Bagside"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -247,19 +229,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>KortID</x:v>
       </x:c>
@@ -270,24 +253,27 @@
         <x:v>Billedsti</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
+        <x:v>Forside</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
         <x:v>Symbol</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>AtomicNumber</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>Dansk</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>Group</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>Hint</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>Bagside</x:v>
       </x:c>
     </x:row>
@@ -305,21 +291,24 @@
         <x:v>H</x:v>
       </x:c>
       <x:c r="E2" s="12" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="G2" s="12" t="str">
         <x:v>Hydrogen</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="H2" s="12" t="str">
         <x:v>Brint</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="I2" s="12" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="J2" s="12" t="str">
         <x:v>Small but dramatic.</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="K2" s="12" t="str">
         <x:v>Hydrogen (H) · atomic number 1</x:v>
       </x:c>
     </x:row>
@@ -337,21 +326,24 @@
         <x:v>He</x:v>
       </x:c>
       <x:c r="E3" s="12" t="str">
+        <x:v>He</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="str">
-        <x:v>Helium</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Helium</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
+        <x:v>Helium</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
         <x:v>Noble gas</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="J3" s="12" t="str">
         <x:v>Makes balloons and voices suspicious.</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="K3" s="12" t="str">
         <x:v>Helium (He) · atomic number 2</x:v>
       </x:c>
     </x:row>
@@ -369,21 +361,24 @@
         <x:v>Li</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
+        <x:v>Li</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="12" t="str">
-        <x:v>Lithium</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>Lithium</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
+        <x:v>Lithium</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
         <x:v>Alkali metal</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="str">
+      <x:c r="J4" s="12" t="str">
         <x:v>Tiny battery celebrity.</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="str">
+      <x:c r="K4" s="12" t="str">
         <x:v>Lithium (Li) · atomic number 3</x:v>
       </x:c>
     </x:row>
@@ -401,21 +396,24 @@
         <x:v>Be</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
+        <x:v>Be</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="12" t="str">
-        <x:v>Beryllium</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>Beryllium</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
+        <x:v>Beryllium</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
         <x:v>Alkaline earth</x:v>
       </x:c>
-      <x:c r="I5" s="12" t="str">
+      <x:c r="J5" s="12" t="str">
         <x:v>Light, stiff and not a snack.</x:v>
       </x:c>
-      <x:c r="J5" s="12" t="str">
+      <x:c r="K5" s="12" t="str">
         <x:v>Beryllium (Be) · atomic number 4</x:v>
       </x:c>
     </x:row>
@@ -433,21 +431,24 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="G6" s="12" t="str">
         <x:v>Boron</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="H6" s="12" t="str">
         <x:v>Bor</x:v>
       </x:c>
-      <x:c r="H6" s="12" t="str">
+      <x:c r="I6" s="12" t="str">
         <x:v>Metalloid</x:v>
       </x:c>
-      <x:c r="I6" s="12" t="str">
+      <x:c r="J6" s="12" t="str">
         <x:v>Boron sounds like boring; it isn't.</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="str">
+      <x:c r="K6" s="12" t="str">
         <x:v>Boron (B) · atomic number 5</x:v>
       </x:c>
     </x:row>
@@ -465,21 +466,24 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
+      <x:c r="G7" s="12" t="str">
         <x:v>Carbon</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
+      <x:c r="H7" s="12" t="str">
         <x:v>Kulstof</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="str">
+      <x:c r="I7" s="12" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="J7" s="12" t="str">
         <x:v>Diamonds, pencils and you.</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="str">
+      <x:c r="K7" s="12" t="str">
         <x:v>Carbon (C) · atomic number 6</x:v>
       </x:c>
     </x:row>
@@ -497,21 +501,24 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
+        <x:v>N</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="str">
+      <x:c r="G8" s="12" t="str">
         <x:v>Nitrogen</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="str">
+      <x:c r="H8" s="12" t="str">
         <x:v>Kvælstof</x:v>
       </x:c>
-      <x:c r="H8" s="12" t="str">
+      <x:c r="I8" s="12" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="J8" s="12" t="str">
         <x:v>Most of the air, very humble.</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="str">
+      <x:c r="K8" s="12" t="str">
         <x:v>Nitrogen (N) · atomic number 7</x:v>
       </x:c>
     </x:row>
@@ -529,21 +536,24 @@
         <x:v>O</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
+        <x:v>O</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
+      <x:c r="G9" s="12" t="str">
         <x:v>Oxygen</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="str">
+      <x:c r="H9" s="12" t="str">
         <x:v>Ilt</x:v>
       </x:c>
-      <x:c r="H9" s="12" t="str">
+      <x:c r="I9" s="12" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="I9" s="12" t="str">
+      <x:c r="J9" s="12" t="str">
         <x:v>Breathing's favorite element.</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="str">
+      <x:c r="K9" s="12" t="str">
         <x:v>Oxygen (O) · atomic number 8</x:v>
       </x:c>
     </x:row>
@@ -561,21 +571,24 @@
         <x:v>F</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
+      <x:c r="G10" s="12" t="str">
         <x:v>Fluorine</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="H10" s="12" t="str">
         <x:v>Fluor</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="str">
+      <x:c r="I10" s="12" t="str">
         <x:v>Halogen</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="str">
+      <x:c r="J10" s="12" t="str">
         <x:v>Toothpaste with attitude.</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="str">
+      <x:c r="K10" s="12" t="str">
         <x:v>Fluorine (F) · atomic number 9</x:v>
       </x:c>
     </x:row>
@@ -593,21 +606,24 @@
         <x:v>Ne</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
+        <x:v>Ne</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Neon</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
         <x:v>Neon</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
+        <x:v>Neon</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
         <x:v>Noble gas</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="J11" s="12" t="str">
         <x:v>Signage influencer.</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="str">
+      <x:c r="K11" s="12" t="str">
         <x:v>Neon (Ne) · atomic number 10</x:v>
       </x:c>
     </x:row>
@@ -625,21 +641,24 @@
         <x:v>Na</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
+        <x:v>Na</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="G12" s="12" t="str">
         <x:v>Sodium</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="H12" s="12" t="str">
         <x:v>Natrium</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="str">
+      <x:c r="I12" s="12" t="str">
         <x:v>Alkali metal</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
+      <x:c r="J12" s="12" t="str">
         <x:v>Salt's dramatic half.</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="str">
+      <x:c r="K12" s="12" t="str">
         <x:v>Sodium (Na) · atomic number 11</x:v>
       </x:c>
     </x:row>
@@ -657,21 +676,24 @@
         <x:v>Mg</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
+        <x:v>Mg</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="F13" s="12" t="str">
-        <x:v>Magnesium</x:v>
       </x:c>
       <x:c r="G13" s="12" t="str">
         <x:v>Magnesium</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str">
+        <x:v>Magnesium</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
         <x:v>Alkaline earth</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="str">
+      <x:c r="J13" s="12" t="str">
         <x:v>Flashy when lit.</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="str">
+      <x:c r="K13" s="12" t="str">
         <x:v>Magnesium (Mg) · atomic number 12</x:v>
       </x:c>
     </x:row>
@@ -689,21 +711,24 @@
         <x:v>Al</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
+        <x:v>Al</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="F14" s="12" t="str">
-        <x:v>Aluminium</x:v>
       </x:c>
       <x:c r="G14" s="12" t="str">
         <x:v>Aluminium</x:v>
       </x:c>
       <x:c r="H14" s="12" t="str">
+        <x:v>Aluminium</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="str">
         <x:v>Post-transition metal</x:v>
       </x:c>
-      <x:c r="I14" s="12" t="str">
+      <x:c r="J14" s="12" t="str">
         <x:v>Foil hat material.</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="str">
+      <x:c r="K14" s="12" t="str">
         <x:v>Aluminium (Al) · atomic number 13</x:v>
       </x:c>
     </x:row>
@@ -721,21 +746,24 @@
         <x:v>Si</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
+        <x:v>Si</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="str">
+      <x:c r="G15" s="12" t="str">
         <x:v>Silicon</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="str">
+      <x:c r="H15" s="12" t="str">
         <x:v>Silicium</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="str">
+      <x:c r="I15" s="12" t="str">
         <x:v>Metalloid</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="str">
+      <x:c r="J15" s="12" t="str">
         <x:v>Computer beach sand.</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="str">
+      <x:c r="K15" s="12" t="str">
         <x:v>Silicon (Si) · atomic number 14</x:v>
       </x:c>
     </x:row>
@@ -753,21 +781,24 @@
         <x:v>P</x:v>
       </x:c>
       <x:c r="E16" s="12" t="str">
+        <x:v>P</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="str">
+      <x:c r="G16" s="12" t="str">
         <x:v>Phosphorus</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="str">
+      <x:c r="H16" s="12" t="str">
         <x:v>Fosfor</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="str">
+      <x:c r="I16" s="12" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="str">
+      <x:c r="J16" s="12" t="str">
         <x:v>Glows in old stories.</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="str">
+      <x:c r="K16" s="12" t="str">
         <x:v>Phosphorus (P) · atomic number 15</x:v>
       </x:c>
     </x:row>
@@ -785,21 +816,24 @@
         <x:v>S</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
+        <x:v>S</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="str">
+      <x:c r="G17" s="12" t="str">
         <x:v>Sulfur</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="str">
+      <x:c r="H17" s="12" t="str">
         <x:v>Svovl</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="str">
+      <x:c r="I17" s="12" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="I17" s="12" t="str">
+      <x:c r="J17" s="12" t="str">
         <x:v>Volcano aroma manager.</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="str">
+      <x:c r="K17" s="12" t="str">
         <x:v>Sulfur (S) · atomic number 16</x:v>
       </x:c>
     </x:row>
@@ -817,21 +851,24 @@
         <x:v>Cl</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
+        <x:v>Cl</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="str">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="str">
+      <x:c r="G18" s="12" t="str">
         <x:v>Chlorine</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="str">
+      <x:c r="H18" s="12" t="str">
         <x:v>Klor</x:v>
       </x:c>
-      <x:c r="H18" s="12" t="str">
+      <x:c r="I18" s="12" t="str">
         <x:v>Halogen</x:v>
       </x:c>
-      <x:c r="I18" s="12" t="str">
+      <x:c r="J18" s="12" t="str">
         <x:v>Pool smell boss.</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="str">
+      <x:c r="K18" s="12" t="str">
         <x:v>Chlorine (Cl) · atomic number 17</x:v>
       </x:c>
     </x:row>
@@ -849,21 +886,24 @@
         <x:v>Ar</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
+        <x:v>Ar</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="str">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="F19" s="12" t="str">
-        <x:v>Argon</x:v>
       </x:c>
       <x:c r="G19" s="12" t="str">
         <x:v>Argon</x:v>
       </x:c>
       <x:c r="H19" s="12" t="str">
+        <x:v>Argon</x:v>
+      </x:c>
+      <x:c r="I19" s="12" t="str">
         <x:v>Noble gas</x:v>
       </x:c>
-      <x:c r="I19" s="12" t="str">
+      <x:c r="J19" s="12" t="str">
         <x:v>Politely refuses to react.</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="str">
+      <x:c r="K19" s="12" t="str">
         <x:v>Argon (Ar) · atomic number 18</x:v>
       </x:c>
     </x:row>
@@ -881,21 +921,24 @@
         <x:v>K</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
+        <x:v>K</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="str">
+      <x:c r="G20" s="12" t="str">
         <x:v>Potassium</x:v>
       </x:c>
-      <x:c r="G20" s="12" t="str">
+      <x:c r="H20" s="12" t="str">
         <x:v>Kalium</x:v>
       </x:c>
-      <x:c r="H20" s="12" t="str">
+      <x:c r="I20" s="12" t="str">
         <x:v>Alkali metal</x:v>
       </x:c>
-      <x:c r="I20" s="12" t="str">
+      <x:c r="J20" s="12" t="str">
         <x:v>Banana chemistry.</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="str">
+      <x:c r="K20" s="12" t="str">
         <x:v>Potassium (K) · atomic number 19</x:v>
       </x:c>
     </x:row>
@@ -913,21 +956,24 @@
         <x:v>Ca</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
+        <x:v>Ca</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F21" s="12" t="str">
-        <x:v>Calcium</x:v>
       </x:c>
       <x:c r="G21" s="12" t="str">
         <x:v>Calcium</x:v>
       </x:c>
       <x:c r="H21" s="12" t="str">
+        <x:v>Calcium</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="str">
         <x:v>Alkaline earth</x:v>
       </x:c>
-      <x:c r="I21" s="12" t="str">
+      <x:c r="J21" s="12" t="str">
         <x:v>Bones approve.</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="str">
+      <x:c r="K21" s="12" t="str">
         <x:v>Calcium (Ca) · atomic number 20</x:v>
       </x:c>
     </x:row>
@@ -945,21 +991,24 @@
         <x:v>Sc</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
+        <x:v>Sc</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="str">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="str">
-        <x:v>Scandium</x:v>
       </x:c>
       <x:c r="G22" s="12" t="str">
         <x:v>Scandium</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str">
+        <x:v>Scandium</x:v>
+      </x:c>
+      <x:c r="I22" s="12" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="I22" s="12" t="str">
+      <x:c r="J22" s="12" t="str">
         <x:v>Rare but Scandinavian-sounding.</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="str">
+      <x:c r="K22" s="12" t="str">
         <x:v>Scandium (Sc) · atomic number 21</x:v>
       </x:c>
     </x:row>
@@ -977,21 +1026,24 @@
         <x:v>Ti</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
+        <x:v>Ti</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="F23" s="12" t="str">
-        <x:v>Titanium</x:v>
       </x:c>
       <x:c r="G23" s="12" t="str">
         <x:v>Titanium</x:v>
       </x:c>
       <x:c r="H23" s="12" t="str">
+        <x:v>Titanium</x:v>
+      </x:c>
+      <x:c r="I23" s="12" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="I23" s="12" t="str">
+      <x:c r="J23" s="12" t="str">
         <x:v>Bike frame flex.</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="str">
+      <x:c r="K23" s="12" t="str">
         <x:v>Titanium (Ti) · atomic number 22</x:v>
       </x:c>
     </x:row>
@@ -1009,21 +1061,24 @@
         <x:v>V</x:v>
       </x:c>
       <x:c r="E24" s="12" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="str">
-        <x:v>Vanadium</x:v>
       </x:c>
       <x:c r="G24" s="12" t="str">
         <x:v>Vanadium</x:v>
       </x:c>
       <x:c r="H24" s="12" t="str">
+        <x:v>Vanadium</x:v>
+      </x:c>
+      <x:c r="I24" s="12" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="I24" s="12" t="str">
+      <x:c r="J24" s="12" t="str">
         <x:v>Sounds like a superhero metal.</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="str">
+      <x:c r="K24" s="12" t="str">
         <x:v>Vanadium (V) · atomic number 23</x:v>
       </x:c>
     </x:row>
@@ -1041,21 +1096,24 @@
         <x:v>Cr</x:v>
       </x:c>
       <x:c r="E25" s="12" t="str">
+        <x:v>Cr</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F25" s="12" t="str">
+      <x:c r="G25" s="12" t="str">
         <x:v>Chromium</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="str">
+      <x:c r="H25" s="12" t="str">
         <x:v>Chrom</x:v>
       </x:c>
-      <x:c r="H25" s="12" t="str">
+      <x:c r="I25" s="12" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="I25" s="12" t="str">
+      <x:c r="J25" s="12" t="str">
         <x:v>Chrome shine.</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="str">
+      <x:c r="K25" s="12" t="str">
         <x:v>Chromium (Cr) · atomic number 24</x:v>
       </x:c>
     </x:row>
@@ -1073,28 +1131,28 @@
         <x:v>Mn</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
+        <x:v>Mn</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F26" s="12" t="str">
+      <x:c r="G26" s="12" t="str">
         <x:v>Manganese</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str">
+      <x:c r="H26" s="12" t="str">
         <x:v>Mangan</x:v>
       </x:c>
-      <x:c r="H26" s="12" t="str">
+      <x:c r="I26" s="12" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="I26" s="12" t="str">
+      <x:c r="J26" s="12" t="str">
         <x:v>Not magnesium's cousin, but close in spelling.</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="str">
+      <x:c r="K26" s="12" t="str">
         <x:v>Manganese (Mn) · atomic number 25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa572eb462b242b7"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/navneleg-demo/periodic-table/periodisk_tabel_demo.xlsx
+++ b/navneleg-demo/periodic-table/periodisk_tabel_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Periodisk tabel" sheetId="1" r:id="R376692e1c723487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PeriodiskTabel" sheetId="1" r:id="R3d8689abcf754058"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2563EB"/>
+        <x:fgColor rgb="FF1D4ED8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -45,30 +45,24 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -78,6 +72,25 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PeriodiskTabelTable" displayName="PeriodiskTabelTable" ref="A1:K26" headerRowCount="1">
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="KortID"/>
+    <x:tableColumn id="2" name="Billedfil"/>
+    <x:tableColumn id="3" name="Billedsti"/>
+    <x:tableColumn id="4" name="Forside"/>
+    <x:tableColumn id="5" name="Symbol"/>
+    <x:tableColumn id="6" name="AtomicNumber"/>
+    <x:tableColumn id="7" name="English"/>
+    <x:tableColumn id="8" name="Dansk"/>
+    <x:tableColumn id="9" name="Group"/>
+    <x:tableColumn id="10" name="Hint"/>
+    <x:tableColumn id="11" name="Bagside"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -229,930 +242,933 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>KortID</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Billedfil</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Billedsti</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Forside</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Symbol</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>AtomicNumber</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Dansk</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Group</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>Hint</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>Bagside</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="10" t="str">
         <x:v>EL001</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>01_hydrogen_h.png</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/01_hydrogen_h.png</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="10" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="10" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="10" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="10" t="str">
         <x:v>Hydrogen</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="10" t="str">
         <x:v>Brint</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="10" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>Small but dramatic.</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
-        <x:v>Hydrogen (H) · atomic number 1</x:v>
+      <x:c r="K2" s="10" t="str">
+        <x:v>Hydrogen</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="10" t="str">
         <x:v>EL002</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>02_helium_he.png</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/02_helium_he.png</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>He</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="E3" s="10" t="str">
         <x:v>He</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>Helium</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>Helium</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>Noble gas</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>Makes balloons and voices suspicious.</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str">
-        <x:v>Helium (He) · atomic number 2</x:v>
+      <x:c r="K3" s="10" t="str">
+        <x:v>Helium</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>EL003</x:v>
       </x:c>
-      <x:c r="B4" s="12" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>03_lithium_li.png</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/03_lithium_li.png</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>Li</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>Li</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>Lithium</x:v>
       </x:c>
-      <x:c r="H4" s="12" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>Lithium</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="str">
+      <x:c r="I4" s="10" t="str">
         <x:v>Alkali metal</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>Tiny battery celebrity.</x:v>
       </x:c>
-      <x:c r="K4" s="12" t="str">
-        <x:v>Lithium (Li) · atomic number 3</x:v>
+      <x:c r="K4" s="10" t="str">
+        <x:v>Lithium</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="12" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>EL004</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>04_beryllium_be.png</x:v>
       </x:c>
-      <x:c r="C5" s="12" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/04_beryllium_be.png</x:v>
       </x:c>
-      <x:c r="D5" s="12" t="str">
+      <x:c r="D5" s="10" t="str">
         <x:v>Be</x:v>
       </x:c>
-      <x:c r="E5" s="12" t="str">
+      <x:c r="E5" s="10" t="str">
         <x:v>Be</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>Beryllium</x:v>
       </x:c>
-      <x:c r="H5" s="12" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>Beryllium</x:v>
       </x:c>
-      <x:c r="I5" s="12" t="str">
+      <x:c r="I5" s="10" t="str">
         <x:v>Alkaline earth</x:v>
       </x:c>
-      <x:c r="J5" s="12" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>Light, stiff and not a snack.</x:v>
       </x:c>
-      <x:c r="K5" s="12" t="str">
-        <x:v>Beryllium (Be) · atomic number 4</x:v>
+      <x:c r="K5" s="10" t="str">
+        <x:v>Beryllium</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="12" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>EL005</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>05_boron_b.png</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/05_boron_b.png</x:v>
       </x:c>
-      <x:c r="D6" s="12" t="str">
+      <x:c r="D6" s="10" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="E6" s="12" t="str">
+      <x:c r="E6" s="10" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>Boron</x:v>
       </x:c>
-      <x:c r="H6" s="12" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>Bor</x:v>
       </x:c>
-      <x:c r="I6" s="12" t="str">
+      <x:c r="I6" s="10" t="str">
         <x:v>Metalloid</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>Boron sounds like boring; it isn't.</x:v>
       </x:c>
-      <x:c r="K6" s="12" t="str">
-        <x:v>Boron (B) · atomic number 5</x:v>
+      <x:c r="K6" s="10" t="str">
+        <x:v>Boron</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>EL006</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>06_carbon_c.png</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/06_carbon_c.png</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="str">
+      <x:c r="D7" s="10" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="str">
+      <x:c r="E7" s="10" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>Carbon</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>Kulstof</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>Diamonds, pencils and you.</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="str">
-        <x:v>Carbon (C) · atomic number 6</x:v>
+      <x:c r="K7" s="10" t="str">
+        <x:v>Carbon</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="12" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>EL007</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>07_nitrogen_n.png</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/07_nitrogen_n.png</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="str">
+      <x:c r="D8" s="10" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="str">
+      <x:c r="E8" s="10" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>Nitrogen</x:v>
       </x:c>
-      <x:c r="H8" s="12" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>Kvælstof</x:v>
       </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="I8" s="10" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>Most of the air, very humble.</x:v>
       </x:c>
-      <x:c r="K8" s="12" t="str">
-        <x:v>Nitrogen (N) · atomic number 7</x:v>
+      <x:c r="K8" s="10" t="str">
+        <x:v>Nitrogen</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>EL008</x:v>
       </x:c>
-      <x:c r="B9" s="12" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>08_oxygen_o.png</x:v>
       </x:c>
-      <x:c r="C9" s="12" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/08_oxygen_o.png</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="str">
+      <x:c r="D9" s="10" t="str">
         <x:v>O</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>O</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
+      <x:c r="F9" s="10" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>Oxygen</x:v>
       </x:c>
-      <x:c r="H9" s="12" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>Ilt</x:v>
       </x:c>
-      <x:c r="I9" s="12" t="str">
+      <x:c r="I9" s="10" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>Breathing's favorite element.</x:v>
       </x:c>
-      <x:c r="K9" s="12" t="str">
-        <x:v>Oxygen (O) · atomic number 8</x:v>
+      <x:c r="K9" s="10" t="str">
+        <x:v>Oxygen</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>EL009</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>09_fluorine_f.png</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/09_fluorine_f.png</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="str">
+      <x:c r="D10" s="10" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>Fluorine</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="str">
+      <x:c r="H10" s="10" t="str">
         <x:v>Fluor</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="str">
+      <x:c r="I10" s="10" t="str">
         <x:v>Halogen</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>Toothpaste with attitude.</x:v>
       </x:c>
-      <x:c r="K10" s="12" t="str">
-        <x:v>Fluorine (F) · atomic number 9</x:v>
+      <x:c r="K10" s="10" t="str">
+        <x:v>Fluorine</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>EL010</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>10_neon_ne.png</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
+      <x:c r="C11" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/10_neon_ne.png</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="str">
+      <x:c r="D11" s="10" t="str">
         <x:v>Ne</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="str">
+      <x:c r="E11" s="10" t="str">
         <x:v>Ne</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="str">
+      <x:c r="F11" s="10" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="str">
+      <x:c r="G11" s="10" t="str">
         <x:v>Neon</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="str">
+      <x:c r="H11" s="10" t="str">
         <x:v>Neon</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="I11" s="10" t="str">
         <x:v>Noble gas</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="str">
+      <x:c r="J11" s="10" t="str">
         <x:v>Signage influencer.</x:v>
       </x:c>
-      <x:c r="K11" s="12" t="str">
-        <x:v>Neon (Ne) · atomic number 10</x:v>
+      <x:c r="K11" s="10" t="str">
+        <x:v>Neon</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="12" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>EL011</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>11_sodium_na.png</x:v>
       </x:c>
-      <x:c r="C12" s="12" t="str">
+      <x:c r="C12" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/11_sodium_na.png</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="str">
+      <x:c r="D12" s="10" t="str">
         <x:v>Na</x:v>
       </x:c>
-      <x:c r="E12" s="12" t="str">
+      <x:c r="E12" s="10" t="str">
         <x:v>Na</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="F12" s="10" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="G12" s="10" t="str">
         <x:v>Sodium</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="str">
+      <x:c r="H12" s="10" t="str">
         <x:v>Natrium</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
+      <x:c r="I12" s="10" t="str">
         <x:v>Alkali metal</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="str">
+      <x:c r="J12" s="10" t="str">
         <x:v>Salt's dramatic half.</x:v>
       </x:c>
-      <x:c r="K12" s="12" t="str">
-        <x:v>Sodium (Na) · atomic number 11</x:v>
+      <x:c r="K12" s="10" t="str">
+        <x:v>Sodium</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="12" t="str">
+      <x:c r="A13" s="10" t="str">
         <x:v>EL012</x:v>
       </x:c>
-      <x:c r="B13" s="12" t="str">
+      <x:c r="B13" s="10" t="str">
         <x:v>12_magnesium_mg.png</x:v>
       </x:c>
-      <x:c r="C13" s="12" t="str">
+      <x:c r="C13" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/12_magnesium_mg.png</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="str">
+      <x:c r="D13" s="10" t="str">
         <x:v>Mg</x:v>
       </x:c>
-      <x:c r="E13" s="12" t="str">
+      <x:c r="E13" s="10" t="str">
         <x:v>Mg</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="str">
+      <x:c r="F13" s="10" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="str">
+      <x:c r="G13" s="10" t="str">
         <x:v>Magnesium</x:v>
       </x:c>
-      <x:c r="H13" s="12" t="str">
+      <x:c r="H13" s="10" t="str">
         <x:v>Magnesium</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="str">
+      <x:c r="I13" s="10" t="str">
         <x:v>Alkaline earth</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="str">
+      <x:c r="J13" s="10" t="str">
         <x:v>Flashy when lit.</x:v>
       </x:c>
-      <x:c r="K13" s="12" t="str">
-        <x:v>Magnesium (Mg) · atomic number 12</x:v>
+      <x:c r="K13" s="10" t="str">
+        <x:v>Magnesium</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="12" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>EL013</x:v>
       </x:c>
-      <x:c r="B14" s="12" t="str">
+      <x:c r="B14" s="10" t="str">
         <x:v>13_aluminium_al.png</x:v>
       </x:c>
-      <x:c r="C14" s="12" t="str">
+      <x:c r="C14" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/13_aluminium_al.png</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="str">
+      <x:c r="D14" s="10" t="str">
         <x:v>Al</x:v>
       </x:c>
-      <x:c r="E14" s="12" t="str">
+      <x:c r="E14" s="10" t="str">
         <x:v>Al</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="str">
+      <x:c r="F14" s="10" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G14" s="12" t="str">
+      <x:c r="G14" s="10" t="str">
         <x:v>Aluminium</x:v>
       </x:c>
-      <x:c r="H14" s="12" t="str">
+      <x:c r="H14" s="10" t="str">
         <x:v>Aluminium</x:v>
       </x:c>
-      <x:c r="I14" s="12" t="str">
+      <x:c r="I14" s="10" t="str">
         <x:v>Post-transition metal</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="str">
+      <x:c r="J14" s="10" t="str">
         <x:v>Foil hat material.</x:v>
       </x:c>
-      <x:c r="K14" s="12" t="str">
-        <x:v>Aluminium (Al) · atomic number 13</x:v>
+      <x:c r="K14" s="10" t="str">
+        <x:v>Aluminium</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="12" t="str">
+      <x:c r="A15" s="10" t="str">
         <x:v>EL014</x:v>
       </x:c>
-      <x:c r="B15" s="12" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>14_silicon_si.png</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="str">
+      <x:c r="C15" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/14_silicon_si.png</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="str">
+      <x:c r="D15" s="10" t="str">
         <x:v>Si</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="str">
+      <x:c r="E15" s="10" t="str">
         <x:v>Si</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="str">
+      <x:c r="F15" s="10" t="str">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="str">
+      <x:c r="G15" s="10" t="str">
         <x:v>Silicon</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="str">
+      <x:c r="H15" s="10" t="str">
         <x:v>Silicium</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="str">
+      <x:c r="I15" s="10" t="str">
         <x:v>Metalloid</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="str">
+      <x:c r="J15" s="10" t="str">
         <x:v>Computer beach sand.</x:v>
       </x:c>
-      <x:c r="K15" s="12" t="str">
-        <x:v>Silicon (Si) · atomic number 14</x:v>
+      <x:c r="K15" s="10" t="str">
+        <x:v>Silicon</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="12" t="str">
+      <x:c r="A16" s="10" t="str">
         <x:v>EL015</x:v>
       </x:c>
-      <x:c r="B16" s="12" t="str">
+      <x:c r="B16" s="10" t="str">
         <x:v>15_phosphorus_p.png</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="str">
+      <x:c r="C16" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/15_phosphorus_p.png</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="str">
+      <x:c r="D16" s="10" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="str">
+      <x:c r="E16" s="10" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="str">
+      <x:c r="F16" s="10" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="str">
+      <x:c r="G16" s="10" t="str">
         <x:v>Phosphorus</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="str">
+      <x:c r="H16" s="10" t="str">
         <x:v>Fosfor</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="str">
+      <x:c r="I16" s="10" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="str">
+      <x:c r="J16" s="10" t="str">
         <x:v>Glows in old stories.</x:v>
       </x:c>
-      <x:c r="K16" s="12" t="str">
-        <x:v>Phosphorus (P) · atomic number 15</x:v>
+      <x:c r="K16" s="10" t="str">
+        <x:v>Phosphorus</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="12" t="str">
+      <x:c r="A17" s="10" t="str">
         <x:v>EL016</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="str">
+      <x:c r="B17" s="10" t="str">
         <x:v>16_sulfur_s.png</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="str">
+      <x:c r="C17" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/16_sulfur_s.png</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="str">
+      <x:c r="D17" s="10" t="str">
         <x:v>S</x:v>
       </x:c>
-      <x:c r="E17" s="12" t="str">
+      <x:c r="E17" s="10" t="str">
         <x:v>S</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="str">
+      <x:c r="F17" s="10" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="str">
+      <x:c r="G17" s="10" t="str">
         <x:v>Sulfur</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="str">
+      <x:c r="H17" s="10" t="str">
         <x:v>Svovl</x:v>
       </x:c>
-      <x:c r="I17" s="12" t="str">
+      <x:c r="I17" s="10" t="str">
         <x:v>Nonmetal</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="str">
+      <x:c r="J17" s="10" t="str">
         <x:v>Volcano aroma manager.</x:v>
       </x:c>
-      <x:c r="K17" s="12" t="str">
-        <x:v>Sulfur (S) · atomic number 16</x:v>
+      <x:c r="K17" s="10" t="str">
+        <x:v>Sulfur</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="12" t="str">
+      <x:c r="A18" s="10" t="str">
         <x:v>EL017</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="str">
+      <x:c r="B18" s="10" t="str">
         <x:v>17_chlorine_cl.png</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="str">
+      <x:c r="C18" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/17_chlorine_cl.png</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="str">
+      <x:c r="D18" s="10" t="str">
         <x:v>Cl</x:v>
       </x:c>
-      <x:c r="E18" s="12" t="str">
+      <x:c r="E18" s="10" t="str">
         <x:v>Cl</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="str">
+      <x:c r="F18" s="10" t="str">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="str">
+      <x:c r="G18" s="10" t="str">
         <x:v>Chlorine</x:v>
       </x:c>
-      <x:c r="H18" s="12" t="str">
+      <x:c r="H18" s="10" t="str">
         <x:v>Klor</x:v>
       </x:c>
-      <x:c r="I18" s="12" t="str">
+      <x:c r="I18" s="10" t="str">
         <x:v>Halogen</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="str">
+      <x:c r="J18" s="10" t="str">
         <x:v>Pool smell boss.</x:v>
       </x:c>
-      <x:c r="K18" s="12" t="str">
-        <x:v>Chlorine (Cl) · atomic number 17</x:v>
+      <x:c r="K18" s="10" t="str">
+        <x:v>Chlorine</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="12" t="str">
+      <x:c r="A19" s="10" t="str">
         <x:v>EL018</x:v>
       </x:c>
-      <x:c r="B19" s="12" t="str">
+      <x:c r="B19" s="10" t="str">
         <x:v>18_argon_ar.png</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="str">
+      <x:c r="C19" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/18_argon_ar.png</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="str">
+      <x:c r="D19" s="10" t="str">
         <x:v>Ar</x:v>
       </x:c>
-      <x:c r="E19" s="12" t="str">
+      <x:c r="E19" s="10" t="str">
         <x:v>Ar</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="str">
+      <x:c r="F19" s="10" t="str">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G19" s="12" t="str">
+      <x:c r="G19" s="10" t="str">
         <x:v>Argon</x:v>
       </x:c>
-      <x:c r="H19" s="12" t="str">
+      <x:c r="H19" s="10" t="str">
         <x:v>Argon</x:v>
       </x:c>
-      <x:c r="I19" s="12" t="str">
+      <x:c r="I19" s="10" t="str">
         <x:v>Noble gas</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="str">
+      <x:c r="J19" s="10" t="str">
         <x:v>Politely refuses to react.</x:v>
       </x:c>
-      <x:c r="K19" s="12" t="str">
-        <x:v>Argon (Ar) · atomic number 18</x:v>
+      <x:c r="K19" s="10" t="str">
+        <x:v>Argon</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="12" t="str">
+      <x:c r="A20" s="10" t="str">
         <x:v>EL019</x:v>
       </x:c>
-      <x:c r="B20" s="12" t="str">
+      <x:c r="B20" s="10" t="str">
         <x:v>19_potassium_k.png</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="str">
+      <x:c r="C20" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/19_potassium_k.png</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="str">
+      <x:c r="D20" s="10" t="str">
         <x:v>K</x:v>
       </x:c>
-      <x:c r="E20" s="12" t="str">
+      <x:c r="E20" s="10" t="str">
         <x:v>K</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="str">
+      <x:c r="F20" s="10" t="str">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G20" s="12" t="str">
+      <x:c r="G20" s="10" t="str">
         <x:v>Potassium</x:v>
       </x:c>
-      <x:c r="H20" s="12" t="str">
+      <x:c r="H20" s="10" t="str">
         <x:v>Kalium</x:v>
       </x:c>
-      <x:c r="I20" s="12" t="str">
+      <x:c r="I20" s="10" t="str">
         <x:v>Alkali metal</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="str">
+      <x:c r="J20" s="10" t="str">
         <x:v>Banana chemistry.</x:v>
       </x:c>
-      <x:c r="K20" s="12" t="str">
-        <x:v>Potassium (K) · atomic number 19</x:v>
+      <x:c r="K20" s="10" t="str">
+        <x:v>Potassium</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="12" t="str">
+      <x:c r="A21" s="10" t="str">
         <x:v>EL020</x:v>
       </x:c>
-      <x:c r="B21" s="12" t="str">
+      <x:c r="B21" s="10" t="str">
         <x:v>20_calcium_ca.png</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="str">
+      <x:c r="C21" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/20_calcium_ca.png</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="str">
+      <x:c r="D21" s="10" t="str">
         <x:v>Ca</x:v>
       </x:c>
-      <x:c r="E21" s="12" t="str">
+      <x:c r="E21" s="10" t="str">
         <x:v>Ca</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="str">
+      <x:c r="F21" s="10" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G21" s="12" t="str">
+      <x:c r="G21" s="10" t="str">
         <x:v>Calcium</x:v>
       </x:c>
-      <x:c r="H21" s="12" t="str">
+      <x:c r="H21" s="10" t="str">
         <x:v>Calcium</x:v>
       </x:c>
-      <x:c r="I21" s="12" t="str">
+      <x:c r="I21" s="10" t="str">
         <x:v>Alkaline earth</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="str">
+      <x:c r="J21" s="10" t="str">
         <x:v>Bones approve.</x:v>
       </x:c>
-      <x:c r="K21" s="12" t="str">
-        <x:v>Calcium (Ca) · atomic number 20</x:v>
+      <x:c r="K21" s="10" t="str">
+        <x:v>Calcium</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="12" t="str">
+      <x:c r="A22" s="10" t="str">
         <x:v>EL021</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="str">
+      <x:c r="B22" s="10" t="str">
         <x:v>21_scandium_sc.png</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="str">
+      <x:c r="C22" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/21_scandium_sc.png</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="str">
+      <x:c r="D22" s="10" t="str">
         <x:v>Sc</x:v>
       </x:c>
-      <x:c r="E22" s="12" t="str">
+      <x:c r="E22" s="10" t="str">
         <x:v>Sc</x:v>
       </x:c>
-      <x:c r="F22" s="12" t="str">
+      <x:c r="F22" s="10" t="str">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G22" s="12" t="str">
+      <x:c r="G22" s="10" t="str">
         <x:v>Scandium</x:v>
       </x:c>
-      <x:c r="H22" s="12" t="str">
+      <x:c r="H22" s="10" t="str">
         <x:v>Scandium</x:v>
       </x:c>
-      <x:c r="I22" s="12" t="str">
+      <x:c r="I22" s="10" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="str">
+      <x:c r="J22" s="10" t="str">
         <x:v>Rare but Scandinavian-sounding.</x:v>
       </x:c>
-      <x:c r="K22" s="12" t="str">
-        <x:v>Scandium (Sc) · atomic number 21</x:v>
+      <x:c r="K22" s="10" t="str">
+        <x:v>Scandium</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="12" t="str">
+      <x:c r="A23" s="10" t="str">
         <x:v>EL022</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="str">
+      <x:c r="B23" s="10" t="str">
         <x:v>22_titanium_ti.png</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="str">
+      <x:c r="C23" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/22_titanium_ti.png</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="str">
+      <x:c r="D23" s="10" t="str">
         <x:v>Ti</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="str">
+      <x:c r="E23" s="10" t="str">
         <x:v>Ti</x:v>
       </x:c>
-      <x:c r="F23" s="12" t="str">
+      <x:c r="F23" s="10" t="str">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="str">
+      <x:c r="G23" s="10" t="str">
         <x:v>Titanium</x:v>
       </x:c>
-      <x:c r="H23" s="12" t="str">
+      <x:c r="H23" s="10" t="str">
         <x:v>Titanium</x:v>
       </x:c>
-      <x:c r="I23" s="12" t="str">
+      <x:c r="I23" s="10" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="str">
+      <x:c r="J23" s="10" t="str">
         <x:v>Bike frame flex.</x:v>
       </x:c>
-      <x:c r="K23" s="12" t="str">
-        <x:v>Titanium (Ti) · atomic number 22</x:v>
+      <x:c r="K23" s="10" t="str">
+        <x:v>Titanium</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="12" t="str">
+      <x:c r="A24" s="10" t="str">
         <x:v>EL023</x:v>
       </x:c>
-      <x:c r="B24" s="12" t="str">
+      <x:c r="B24" s="10" t="str">
         <x:v>23_vanadium_v.png</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="str">
+      <x:c r="C24" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/23_vanadium_v.png</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="str">
+      <x:c r="D24" s="10" t="str">
         <x:v>V</x:v>
       </x:c>
-      <x:c r="E24" s="12" t="str">
+      <x:c r="E24" s="10" t="str">
         <x:v>V</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="str">
+      <x:c r="F24" s="10" t="str">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="str">
+      <x:c r="G24" s="10" t="str">
         <x:v>Vanadium</x:v>
       </x:c>
-      <x:c r="H24" s="12" t="str">
+      <x:c r="H24" s="10" t="str">
         <x:v>Vanadium</x:v>
       </x:c>
-      <x:c r="I24" s="12" t="str">
+      <x:c r="I24" s="10" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="str">
+      <x:c r="J24" s="10" t="str">
         <x:v>Sounds like a superhero metal.</x:v>
       </x:c>
-      <x:c r="K24" s="12" t="str">
-        <x:v>Vanadium (V) · atomic number 23</x:v>
+      <x:c r="K24" s="10" t="str">
+        <x:v>Vanadium</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="12" t="str">
+      <x:c r="A25" s="10" t="str">
         <x:v>EL024</x:v>
       </x:c>
-      <x:c r="B25" s="12" t="str">
+      <x:c r="B25" s="10" t="str">
         <x:v>24_chromium_cr.png</x:v>
       </x:c>
-      <x:c r="C25" s="12" t="str">
+      <x:c r="C25" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/24_chromium_cr.png</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="str">
+      <x:c r="D25" s="10" t="str">
         <x:v>Cr</x:v>
       </x:c>
-      <x:c r="E25" s="12" t="str">
+      <x:c r="E25" s="10" t="str">
         <x:v>Cr</x:v>
       </x:c>
-      <x:c r="F25" s="12" t="str">
+      <x:c r="F25" s="10" t="str">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="str">
+      <x:c r="G25" s="10" t="str">
         <x:v>Chromium</x:v>
       </x:c>
-      <x:c r="H25" s="12" t="str">
+      <x:c r="H25" s="10" t="str">
         <x:v>Chrom</x:v>
       </x:c>
-      <x:c r="I25" s="12" t="str">
+      <x:c r="I25" s="10" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="str">
+      <x:c r="J25" s="10" t="str">
         <x:v>Chrome shine.</x:v>
       </x:c>
-      <x:c r="K25" s="12" t="str">
-        <x:v>Chromium (Cr) · atomic number 24</x:v>
+      <x:c r="K25" s="10" t="str">
+        <x:v>Chromium</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="12" t="str">
+      <x:c r="A26" s="10" t="str">
         <x:v>EL025</x:v>
       </x:c>
-      <x:c r="B26" s="12" t="str">
+      <x:c r="B26" s="10" t="str">
         <x:v>25_manganese_mn.png</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="str">
+      <x:c r="C26" s="10" t="str">
         <x:v>navneleg-demo/periodic-table/photos/25_manganese_mn.png</x:v>
       </x:c>
-      <x:c r="D26" s="12" t="str">
+      <x:c r="D26" s="10" t="str">
         <x:v>Mn</x:v>
       </x:c>
-      <x:c r="E26" s="12" t="str">
+      <x:c r="E26" s="10" t="str">
         <x:v>Mn</x:v>
       </x:c>
-      <x:c r="F26" s="12" t="str">
+      <x:c r="F26" s="10" t="str">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str">
+      <x:c r="G26" s="10" t="str">
         <x:v>Manganese</x:v>
       </x:c>
-      <x:c r="H26" s="12" t="str">
+      <x:c r="H26" s="10" t="str">
         <x:v>Mangan</x:v>
       </x:c>
-      <x:c r="I26" s="12" t="str">
+      <x:c r="I26" s="10" t="str">
         <x:v>Transition metal</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="str">
+      <x:c r="J26" s="10" t="str">
         <x:v>Not magnesium's cousin, but close in spelling.</x:v>
       </x:c>
-      <x:c r="K26" s="12" t="str">
-        <x:v>Manganese (Mn) · atomic number 25</x:v>
+      <x:c r="K26" s="10" t="str">
+        <x:v>Manganese</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74856bd6519d4df2"/>
+  </x:tableParts>
 </x:worksheet>
 </file>